--- a/RS1_HKRN_KIKI_DEV_GT-26.xlsx
+++ b/RS1_HKRN_KIKI_DEV_GT-26.xlsx
@@ -1606,35 +1606,35 @@
     <row r="73">
       <c r="B73" t="inlineStr">
         <is>
-          <t>先行開発時には、既存コード、日本側から提供されたSymbolおよび先行開発時に参照したガイドを根拠として、動的SQLにより切り替わる「=」および「IN」の生成有無を中心に確認する構成としました。</t>
+          <t>先行開発時は、既存コード、日本側から提供されたSymbolおよび先行開発時に参照したガイドを参照し、動的SQLによって切り替わる「=」および「IN」の生成有無を中心に確認する構成としました。</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="inlineStr">
         <is>
-          <t>先行開発時に参照したガイドを確認した範囲では、本格開発で使用するガイドに記載されているSELECT句、JOIN、GROUP BY、ORDER BYおよび各UNION部分等について、SQL構成要素ごとに詳細な確認を実施する旨の明示的な記載は確認できませんでした。</t>
+          <t>先行開発時に参照したガイドでは、本格開発で使用するガイドに記載されているSELECT句、JOIN、GROUP BY、ORDER BYおよび各UNION部分等について、SQL構成要素ごとに詳細な確認を実施することまでは明確に求められていませんでした。</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
         <is>
-          <t>先行開発で作成したJUnitでは、主要な動的SQLの生成条件に加え、実DBにおけるDAOの検索結果、取得したDTOおよび並び順を確認しています。SQL構成要素ごとの詳細確認とは範囲が異なりますが、先行開発時に求められた動的SQLおよびDAO実行結果の確認を実施しています。</t>
+          <t>先行開発で作成したJUnitでは、主要な動的SQLの生成条件に加えて、実DBでのDAO検索結果、取得DTOおよび並び順を確認しており、対象SQLの主要な動作は検証できています。</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t>本格開発で使用するガイドに記載されたSQL構成要素ごとの確認は、本格開発で新規に作成するMapperおよびDAOのJUnitに適用します。先行開発成果への遡及適用は、各SQLの構成要素の再整理、検証処理およびテストデータの見直しならびに再検証を要するため、行いません。</t>
+          <t>本格開発で使用するガイドに合わせて確認項目を追加する場合、既存Mapperの各SQLについて構成要素を再整理し、検証処理およびテストデータを追加する必要があります。</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
-          <t>以上より、先行開発で作成済みのMapperおよびDAOのJUnitは、先行開発時に提供されたガイド、Symbolおよび既存コードを根拠として実装し、当時の確認範囲に対応する検証を実施しているため、本格開発で使用するガイドを遡及適用せず、既存実装を維持します。本格開発で新規に作成するMapperおよびDAOのJUnitは、本格開発で使用するガイドに従って実施します。</t>
+          <t>そのため、先行開発で作成済みのDAO JUnitについては先行開発時の確認範囲を維持し、本格開発で新規に作成または大きく変更するMapperおよびDAO JUnitから本格開発で使用するガイドを適用してよいか、ご確認をお願いいたします。</t>
         </is>
       </c>
     </row>
@@ -1796,28 +1796,28 @@
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>先行開発時は、既存コード、日本側から提供されたSymbolおよび先行開発時に参照したガイドを踏まえて実装しました。</t>
+          <t>先行開発時は、既存コード、日本側から提供されたSymbolおよび先行開発時に参照したガイドを参照して実装しました。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>先行開発時に参照したガイドでは、外部依存先の戻り値をMockで設定し、外部依存先のメソッドの呼出有無および呼出回数を検証する実装パターンが示されていました。</t>
+          <t>先行開発時に参照したガイドでは、外部部品の戻り値をMockで定義し、対象メソッドが期待どおり呼び出されているか、および期待した回数だけ呼び出されているかを検証する実装パターンが示されていました。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>一方、先行開発時に参照したガイドを確認した範囲では、外部依存先へ渡す引数の内容を必ず詳細に検証する旨の記載は確認できませんでした。</t>
+          <t>一方、外部部品へ渡す実際の引数について、必ず詳細に検証する旨は明記されていませんでした。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>先行開発時は、先行開発時に参照したガイドおよび既存実装を踏まえ、外部依存先の呼出有無および呼出回数を中心に検証し、呼出引数にはany()を使用しました。本格開発で使用するガイドにおける呼出引数の詳細検証は、先行開発時には明示されていなかった追加の確認観点であるため、先行開発で作成済みのJUnitには遡及追加しません。本格開発で新規に作成するJUnitは、本格開発で使用するガイドに従い、呼出引数、呼出回数および未呼出を検証します。</t>
+          <t>そのため、先行開発時は先行開発時に参照したガイドに従い、呼出回数を中心に検証し、呼出引数にはany()を使用しました。</t>
         </is>
       </c>
     </row>
@@ -7393,28 +7393,28 @@
     <row r="69">
       <c r="B69" t="inlineStr">
         <is>
-          <t>先行開発時は、既存コード、日本側から提供されたSymbolおよび先行開発時に参照したガイドを根拠として、検索条件と単純な期待値を各テストケースのJavaコード内で管理する構成としました。</t>
+          <t>先行開発時は、既存コード、日本側から提供されたSymbolおよび先行開発時に参照したガイドを参照し、DBの前提データはCSV、DAOメソッドへ渡す検索条件は各CaseのJavaコード内で管理する構成としました。また、複雑なDTOはCSV、単純なListおよび件数はJavaコード内で確認する構成としました。</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="inlineStr">
         <is>
-          <t>先行開発で作成したテストコードでは、検索条件と単純な期待値を各テストケース内で直接確認し、DAOメソッドの検索結果および動的SQLの生成内容を検証しています。</t>
+          <t>先行開発時の構成では、各Caseの検索条件および単純な期待値をテストコード上で直接確認でき、入力条件と実行結果の対応も把握しやすくなっています。また、DAO検索結果、動的SQLの生成内容、0件、1件および業種コードListも問題なく検証できています。</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
         <is>
-          <t>本格開発で使用するガイドとの差異は、主として検索条件および期待値のテストデータ管理方式にあります。先行開発時のJUnitでは、検索条件と単純な期待値を各テストケース内で直接確認し、DAOメソッドの検索結果および動的SQLの生成内容を検証しています。CSV管理への遡及移行には、入力値・期待値CSVおよび読み込み処理の追加、既存JUnitの修正ならびに再検証が必要となります。</t>
+          <t>検索条件および単純な期待値をCSVへ移行しても、テスト内容、確認内容および検証結果自体は変わらず、Caseごとの入力・期待値CSVと読込処理を追加する対応になると考えています。</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="inlineStr">
         <is>
-          <t>以上より、先行開発で作成済みのDAOのJUnitは先行開発時の管理方法を維持し、CSV管理への遡及移行は行いません。本格開発で新規に作成するDAOのJUnitは、本格開発で使用するガイドに従って検索条件および期待値を管理します。</t>
+          <t>そのため、先行開発で作成済みのDAO JUnitについては先行開発時の検索条件および期待値の管理方法を維持し、本格開発で新規に作成するDAO JUnitから本格開発で使用するガイドを適用してよいか、ご確認をお願いいたします。</t>
         </is>
       </c>
     </row>
@@ -7625,28 +7625,28 @@
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>先行開発時は、既存コード、日本側から提供されたSymbolおよび先行開発時に参照したガイドを根拠として、当該ガイドに示されたディレクトリ構成およびファイル配置に従って作成しました。</t>
+          <t>先行開発時は、既存コード、日本側から提供されたSymbolおよび先行開発時に参照したガイドを参照し、先行開発時に示されていたディレクトリ構成およびファイル配置に従って作成しました。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>先行開発で採用した01_inputdata、commonおよび03_actualを使用する構成では、テストケースごとのDB投入用前提データおよび期待値CSVを管理し、DAOの実行結果を検証しています。</t>
+          <t>先行開発時の01_inputdata、commonおよび03_actualを使用した構成でも、CaseごとのDB前提データと期待値を管理できており、DAOの実行結果も問題なく検証できています。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>本格開発で使用するガイドとの差異は、主としてテストデータおよび期待値の管理場所、名称ならびにディレクトリ構成です。先行開発で作成済みのJUnitでは、DB投入用前提データおよび期待値CSVを用いてDAOの実行結果を検証しています。ガイド形式の遡及適用には、既存CSVの移動・名称変更、Javaコード内のパス修正および再検証が必要となります。</t>
+          <t>本格開発で使用するガイド形式へ変更しても、テストデータおよび検証内容自体は変わらず、既存CSVの移動、名称変更およびJavaコード内のパス修正が必要となります。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>以上より、先行開発で作成済みのDAOのJUnitは、先行開発時のディレクトリ構成を維持し、本格開発で使用するガイドの構成へ遡及変更しません。本格開発で新規に作成するDAOのJUnitは、本格開発で使用するガイドに従って作成します。</t>
+          <t>そのため、先行開発で作成済みのDAO JUnitについては先行開発時のディレクトリ構成を維持し、本格開発で新規に作成するDAO JUnitから本格開発で使用するガイドを適用してよいか、ご確認をお願いいたします。</t>
         </is>
       </c>
     </row>
@@ -7836,35 +7836,35 @@
     <row r="34">
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>先行開発時は、Symbol、既存コードおよび先行開発時に参照したガイドを踏まえ、各Search_Dialog系TestBaseを継承する構成で実装しました。</t>
+          <t>先行開発時は、Symbol、既存コードおよび先行開発時に参照したガイドを参照し、記載されていた方式に従って各Search_Dialog系TestBaseを継承する構成で実装しました。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>一方、本格開発で使用するガイドには、Dao JUnit／Logic JUnitともに、先行開発時の実装とは異なるTestBaseを直接継承する構成が記載されています。</t>
+          <t>一方、本格開発で使用するガイドでは、Dao／Logicともに別のTestBaseを直接継承する構成が記載されており、先行開発時に参照した規定内容と異なっています。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>また、本格開発で使用するGitリポジトリ上で確認した範囲では、ガイドに記載されているDAA_DaoTestBaseおよびDAA_LogicTestBaseは存在しません。</t>
+          <t>また、本格開発で使用するガイドに記載されているDAA_DaoTestBaseおよびDAA_LogicTestBaseは、本格開発のGit環境には存在しません。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>本格開発で使用するGitリポジトリ上で確認した範囲では、ガイドに記載されたDAA_DaoTestBaseおよびDAA_LogicTestBaseは存在しません。先行開発で作成済みのJUnitは、当時のSymbol、既存コードおよび参照ガイドに基づくSearch_Dialog系TestBaseの継承により実装しているため、継承元を遡及変更せず、既存実装を維持します。本格開発で新規に作成するJUnitは、利用可能な本格開発環境の基底クラスおよびガイドに従って実装します。</t>
+          <t>そのため、本格開発のGit環境でガイド記載の継承元へ変更するとコンパイルエラーが発生し、ガイドに記載された構成をそのまま適用できない状態です。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>本件については、既にQAを起票済みです。</t>
+          <t>本件については、すでにQAを提出しています。</t>
         </is>
       </c>
     </row>
@@ -8022,28 +8022,28 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>先行開発時は、Symbol、既存コードおよび先行開発時に参照したガイドを踏まえ、テストクラス内にBaseを定義しました。</t>
+          <t>先行開発時は、Symbol、既存コードおよび先行開発時に参照したガイドを参照し、記載されていた構成や実装方法に従って、テストクラス内にBaseを定義しました。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>一方、本格開発で使用するガイドでは独自Baseを作成しない構成が示されており、先行開発時に参照した資料および先行開発時の既存実装と差異があります。</t>
+          <t>一方、本格開発で使用するガイドでは独自Baseを作成しない構成が示されており、先行開発時に参照した資料および既存の実装方法と異なっています。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>また、本格開発で使用するGitリポジトリ上で確認した範囲では、ガイドに記載のDAA_LogicTestBaseを確認できないため、先行開発時に定義したBaseがMock、Weldおよび共通初期化処理を集約する役割も担っています。</t>
+          <t>また、先行開発時に定義したBaseは、ガイドに記載されているDAA_LogicTestBaseが本格開発のGit環境に存在しないため、Mock、Weldおよび共通初期化処理をまとめる役割も担っています。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>先行開発で作成済みのJUnitでは、当時のSymbol、既存コードおよび参照ガイドに基づき、独自BaseがMock、Weldおよび共通初期化処理を集約しています。本格開発で使用するガイドとの差異は、主として継承構造およびコード組織上の実装方式にあるため、独自Baseを廃止する遡及変更は行わず、既存実装を維持します。本格開発で新規に作成するJUnitは、本格開発で使用するガイドに従い、独自Baseを作成しない構成とします。</t>
+          <t>本項目は「4. Dao・Logic JUnit継承元」と関連するため、同項目のQAと併せて対応方針をご確認いただきたいです。</t>
         </is>
       </c>
     </row>
@@ -8057,7 +8057,7 @@
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>「4. Dao・Logic JUnit継承元」に記載のQAをご参照ください。</t>
+          <t>「4. Dao・Logic JUnit継承元」と同一のQAを参照</t>
         </is>
       </c>
     </row>
@@ -8766,28 +8766,28 @@
     <row r="107">
       <c r="B107" t="inlineStr">
         <is>
-          <t>通常の入力DTO等をCSVで管理し、List型等の一部データのみをJavaコード内で管理する場合は、同一テストクラス内で管理方法が混在します。この混在が確認および保守に与える影響を考慮しました。</t>
+          <t>そのため、通常の入力DTO等をCSVで管理し、List型等の一部データのみをJavaコード内で管理すると、同一テストクラス内で管理方法が混在し、確認および保守が複雑になると判断しました。</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" t="inlineStr">
         <is>
-          <t>この点については、先行開発時の内部レビューで検討した結果、管理方法を統一するため、入力値、Mockの戻り値および期待値をJavaコード内で管理する方針としました。</t>
+          <t>この点について内部レビュー担当者等と検討した結果、管理方法を統一するため、入力値、Mock戻り値および期待値をJavaコード内で管理する方針としました。</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" t="inlineStr">
         <is>
-          <t>本格開発で使用するガイドでは、List型を含むデータをCSVで管理する方法が示されています。一方、先行開発時のJUnitでは、入力値、Mockの戻り値および期待値をJavaコード内で一元管理し、テスト対象メソッドの実行結果および外部依存に関する検証を実施しています。差異は主としてデータ管理およびコード構成の方式にあります。</t>
+          <t>本格開発で使用するガイドではList型を含むCSV管理方法が示されていますが、先行開発時の実装でも同等のテストおよび検証を実施できていると認識しています。</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" t="inlineStr">
         <is>
-          <t>既存の入力値、Mockの戻り値および期待値をCSV管理へ移行するには、対象範囲の整理、CSVおよび読み込み処理の追加、JUnitの修正ならびに再検証が必要となります。このため、先行開発成果には本格開発で使用するガイドを遡及適用せず、先行開発時の管理方法を維持します。本格開発で新規に作成するJUnitは、本格開発で使用するガイドに従います。</t>
+          <t>また、既存の入力値、Mock戻り値および期待値をすべてCSVへ移行する場合、修正範囲および作業量が大きくなるため、先行開発時の管理方法を継続してよいか、ご確認をお願いいたします。</t>
         </is>
       </c>
     </row>
@@ -9181,35 +9181,35 @@
     <row r="75">
       <c r="B75" t="inlineStr">
         <is>
-          <t>先行開発時には、既存コード、日本側から提供されたSymbolおよび先行開発時に参照したガイドを踏まえ、Mockの設定、入力値および期待値の作成、テスト対象メソッドの実行ならびに検証を各テストケース内に記載する構成で実装しました。</t>
+          <t>先行開発時は、既存コード、日本側から提供されたSymbolおよび先行開発時に参照したガイドを参照し、Mock設定、入力、期待値、実行および検証を各Case内に記載する構成で実装しました。</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t>本格開発で使用するガイドの例では、Test、Data、ArrangeおよびAssertionsに相当する処理を共通メソッドに分け、各@TestメソッドからexecuteCaseを呼び出す構成となっており、先行開発時の実装方式とは異なります。</t>
+          <t>本格開発で使用するガイド例では、Test、Data、ArrangeおよびAssertionsに相当する処理を共通メソッドへ分け、各@TestからexecuteCaseを呼び出す構成となっており、先行開発時の実装方式と異なっています。</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
-          <t>先行開発時の実装では、当時参照した資料に基づき、各テストケース内でMock設定、入力値・期待値の作成、対象メソッドの実行および検証を区分して記載し、戻り値と外部依存を検証しています。</t>
+          <t>ただし、先行開発時の実装でも各Case内で処理内容を明確に区分しており、必要なテストおよび検証を実施できています。</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="inlineStr">
         <is>
-          <t>本格開発で使用するガイドとの差異は、主としてJUnit内の処理配置および共通メソッドへの分割方法です。先行開発時のJUnitでも一連のテスト処理を各テストケース内で実施しており、ガイド形式への遡及移行はJUnitの広範な再構成および再検証を伴うため、既存JUnitは当該形式へ移行しません。</t>
+          <t>テスト内容や検証結果に差異がなく、主にJUnit内部の記載方法および構成を変更する対応となるため、既存JUnitをガイド例の形式へ移行する必要はないと考えています。</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="inlineStr">
         <is>
-          <t>先行開発で作成済みのJUnitは既存構成を維持します。本格開発で新規に作成するJUnitは、本格開発で使用するガイドに従い、Test、Data、ArrangeおよびAssertionsに相当する処理を共通メソッドに分けて実装します。</t>
+          <t>先行開発時の実装を変更せず、先行開発時の構成を継続してよいか、ご確認をお願いいたします。</t>
         </is>
       </c>
     </row>
@@ -9574,28 +9574,28 @@
     <row r="73">
       <c r="B73" t="inlineStr">
         <is>
-          <t>先行開発時には、カバレッジレポートに未通過箇所を残さない要件に対応するため、通常のテストケースで実行されない一部の分岐に対し、カバレッジ専用ケースを追加しました。</t>
+          <t>先行開発時は、単体テストのカバレッジレポートをすべて通過させる必要があったため、通常のテストケースでは実行されない細かな分岐に対して、Coverage専用ケースを追加しました。</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="inlineStr">
         <is>
-          <t>一部の先行開発ケースでは、DTOをSpy化し、同一のGetterから異なる値を順に返す設定により、先行開発時のカバレッジ要件に対応しています。本格開発で使用するガイドとの差異は、カバレッジ専用ケースの取扱いおよびDTOのSpy化というテスト実装・運用上の方針にあります。</t>
+          <t>Coverage専用ケースを追加すること自体ではなく、一部のケースにおいて、DTOをSpy化し、同一Getterから異なる値を順番に返すことで、通常の入力状態では到達しない分岐を実行している点が、本格開発で使用するガイドの方針と異なっています。</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
         <is>
-          <t>当該ケースは、先行開発時にカバレッジレポート上の未通過箇所を残さない要件へ対応するために追加したものです。削除または再構成にはカバレッジ結果の再確認および既存JUnitの再検証を伴うため、先行開発で作成済みのカバレッジ専用ケースは変更しません。</t>
+          <t>一方、当該ケースを削除した場合、先行開発時に必須とされていたカバレッジレポートに未通過箇所が発生します。</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t>以上より、先行開発で作成済みのカバレッジ専用ケース（DTOのSpy化を含む）は、先行開発時のカバレッジ要件に基づく実装として維持し、本格開発で使用するガイドを遡及適用しません。本格開発で新規に作成するJUnitは、本格開発で使用するガイドに従って実装します。</t>
+          <t>そのため、先行開発時のカバレッジ要件を優先し、Coverage専用ケースを先行開発時の実装のまま残してよいか、ご確認をお願いいたします。</t>
         </is>
       </c>
     </row>
